--- a/output/pdf_financials_xlsx/LEM.xlsx
+++ b/output/pdf_financials_xlsx/LEM.xlsx
@@ -5588,28 +5588,28 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.660868</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.664512</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.995583</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.13581</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.15281</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.757294</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.502888</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.611413</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -11623,7 +11623,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.660868</v>
       </c>

--- a/output/pdf_financials_xlsx/LEM.xlsx
+++ b/output/pdf_financials_xlsx/LEM.xlsx
@@ -1098,22 +1098,22 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.079767</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.01389</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.025497</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.061492</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.097375</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.055336</v>
       </c>
     </row>
     <row r="13">
@@ -2120,13 +2120,13 @@
         <v>-11.117407</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.721821</v>
+        <v>-1.801588</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.210718</v>
+        <v>-1.224608</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.610532</v>
+        <v>-3.636029</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.687724</v>
+        <v>-2.785099</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.216565</v>
+        <v>-3.271901</v>
       </c>
     </row>
     <row r="28">
@@ -2248,13 +2248,13 @@
         <v>-11.084711</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.697597</v>
+        <v>-1.777364</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.177013</v>
+        <v>-1.190903</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.586463</v>
+        <v>-3.61196</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.656261</v>
+        <v>-2.753636</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.132178</v>
+        <v>-3.187514</v>
       </c>
     </row>
     <row r="30">
@@ -2512,49 +2512,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.864677</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>16.863409</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>11.438553</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>6.506217</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.214185</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.698836</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.979914</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.18442</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.395609</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.361424</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.316797</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.198536</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.427311</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.460217</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.860654</v>
       </c>
     </row>
     <row r="35">
@@ -2616,49 +2616,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.864677</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>16.863409</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>11.438553</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>6.506217</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.214185</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.698836</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.979914</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.18442</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.395609</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.361424</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.316797</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.198536</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.427311</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.460217</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.860654</v>
       </c>
     </row>
     <row r="37">
@@ -3240,49 +3240,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.874317</v>
+        <v>0.009639999999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>17.108392</v>
+        <v>0.244983</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>11.595091</v>
+        <v>0.156538</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6.848209</v>
+        <v>0.341992</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.353169</v>
+        <v>0.138984</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.944991</v>
+        <v>0.246155</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.37146</v>
+        <v>0.391546</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.485498</v>
+        <v>0.301078</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.631656</v>
+        <v>0.236047</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.635252</v>
+        <v>0.273828</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.471356</v>
+        <v>1.154559</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.491918</v>
+        <v>0.293382</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.965275</v>
+        <v>0.537964</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.901806</v>
+        <v>0.441589</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.277571</v>
+        <v>0.416917</v>
       </c>
     </row>
     <row r="49">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8964,7 +8964,11 @@
           <t>Reclamation deposit 7</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -10753,7 +10757,11 @@
           <t>Reclamation deposit 6</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11977,7 +11985,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
@@ -12250,7 +12258,11 @@
           <t>Reclamation deposit 8</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -12889,7 +12901,11 @@
           <t>Reclamation deposit 9</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>0.076462</v>
       </c>
@@ -25021,7 +25037,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -27264,7 +27280,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -29476,7 +29492,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">

--- a/output/pdf_financials_xlsx/LEM.xlsx
+++ b/output/pdf_financials_xlsx/LEM.xlsx
@@ -6780,10 +6780,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.012644</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.008508</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -17627,7 +17627,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
